--- a/Omset Kategori-2026-02.xlsx
+++ b/Omset Kategori-2026-02.xlsx
@@ -626,8 +626,12 @@
   <cols>
     <col min="1" max="1" width="2.75" customWidth="1"/>
     <col min="2" max="2" width="17.6875" customWidth="1"/>
-    <col min="3" max="9" width="9.5625" customWidth="1"/>
-    <col min="10" max="30" width="10" customWidth="1"/>
+    <col min="3" max="6" width="9.5625" customWidth="1"/>
+    <col min="7" max="11" width="10" customWidth="1"/>
+    <col min="12" max="12" width="11" customWidth="1"/>
+    <col min="13" max="17" width="10" customWidth="1"/>
+    <col min="18" max="19" width="11" customWidth="1"/>
+    <col min="20" max="30" width="10" customWidth="1"/>
     <col min="31" max="31" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1005,7 +1009,7 @@
         <v>0</v>
       </c>
       <c r="L9" s="12">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="M9" s="12">
         <v>0</v>
@@ -1063,7 +1067,7 @@
       </c>
       <c r="AE9" s="13">
         <f>SUM(C9:AD9)</f>
-        <v>0</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.25">
@@ -1086,13 +1090,13 @@
         <v>0</v>
       </c>
       <c r="G10" s="12">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="H10" s="12">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="I10" s="12">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="J10" s="12">
         <v>0</v>
@@ -1101,16 +1105,16 @@
         <v>0</v>
       </c>
       <c r="L10" s="12">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="M10" s="12">
         <v>0</v>
       </c>
       <c r="N10" s="12">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="O10" s="12">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="P10" s="12">
         <v>0</v>
@@ -1125,13 +1129,13 @@
         <v>0</v>
       </c>
       <c r="T10" s="12">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="U10" s="12">
         <v>0</v>
       </c>
       <c r="V10" s="12">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="W10" s="12">
         <v>0</v>
@@ -1152,14 +1156,14 @@
         <v>0</v>
       </c>
       <c r="AC10" s="12">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="AD10" s="12">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="AE10" s="13">
         <f>SUM(C10:AD10)</f>
-        <v>0</v>
+        <v>440000</v>
       </c>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.25">
@@ -1192,61 +1196,61 @@
         <v>0</v>
       </c>
       <c r="H12" s="12">
-        <v>0</v>
+        <v>360000</v>
       </c>
       <c r="I12" s="12">
-        <v>0</v>
+        <v>210000</v>
       </c>
       <c r="J12" s="12">
-        <v>0</v>
+        <v>210000</v>
       </c>
       <c r="K12" s="12">
-        <v>0</v>
+        <v>330000</v>
       </c>
       <c r="L12" s="12">
-        <v>0</v>
+        <v>240000</v>
       </c>
       <c r="M12" s="12">
-        <v>0</v>
+        <v>270000</v>
       </c>
       <c r="N12" s="12">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="O12" s="12">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="P12" s="12">
         <v>0</v>
       </c>
       <c r="Q12" s="12">
-        <v>0</v>
+        <v>240000</v>
       </c>
       <c r="R12" s="12">
-        <v>0</v>
+        <v>450000</v>
       </c>
       <c r="S12" s="12">
-        <v>0</v>
+        <v>360000</v>
       </c>
       <c r="T12" s="12">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="U12" s="12">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="V12" s="12">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="W12" s="12">
-        <v>0</v>
+        <v>180000</v>
       </c>
       <c r="X12" s="12">
-        <v>0</v>
+        <v>180000</v>
       </c>
       <c r="Y12" s="12">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="Z12" s="12">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="AA12" s="12">
         <v>0</v>
@@ -1255,14 +1259,14 @@
         <v>0</v>
       </c>
       <c r="AC12" s="12">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="AD12" s="12">
         <v>0</v>
       </c>
       <c r="AE12" s="13">
         <f>SUM(C12:AD12)</f>
-        <v>0</v>
+        <v>3750000</v>
       </c>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.25">
@@ -1298,65 +1302,65 @@
         <v>0</v>
       </c>
       <c r="L13" s="12">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="M13" s="12">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="N13" s="12">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="O13" s="12">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="P13" s="12">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="Q13" s="12">
         <v>0</v>
       </c>
       <c r="R13" s="12">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="S13" s="12">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="T13" s="12">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="U13" s="12">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="V13" s="12">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="W13" s="12">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="X13" s="12">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="Y13" s="12">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="Z13" s="12">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="AA13" s="12">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="AB13" s="12">
         <v>0</v>
       </c>
       <c r="AC13" s="12">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="AD13" s="12">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="AE13" s="13">
         <f>SUM(C13:AD13)</f>
-        <v>0</v>
+        <v>3150000</v>
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.25">
@@ -1439,7 +1443,7 @@
         <v>0</v>
       </c>
       <c r="AA14" s="12">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="AB14" s="12">
         <v>0</v>
@@ -1452,7 +1456,7 @@
       </c>
       <c r="AE14" s="13">
         <f>SUM(C14:AD14)</f>
-        <v>0</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.25">
@@ -1475,16 +1479,16 @@
         <v>0</v>
       </c>
       <c r="G15" s="12">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="H15" s="12">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="I15" s="12">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="J15" s="12">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="K15" s="12">
         <v>0</v>
@@ -1496,25 +1500,25 @@
         <v>0</v>
       </c>
       <c r="N15" s="12">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="O15" s="12">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="P15" s="12">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="Q15" s="12">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="R15" s="12">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="S15" s="12">
         <v>0</v>
       </c>
       <c r="T15" s="12">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="U15" s="12">
         <v>0</v>
@@ -1529,7 +1533,7 @@
         <v>0</v>
       </c>
       <c r="Y15" s="12">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="Z15" s="12">
         <v>0</v>
@@ -1541,14 +1545,14 @@
         <v>0</v>
       </c>
       <c r="AC15" s="12">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="AD15" s="12">
         <v>0</v>
       </c>
       <c r="AE15" s="13">
         <f>SUM(C15:AD15)</f>
-        <v>0</v>
+        <v>420000</v>
       </c>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.25">
@@ -1571,80 +1575,80 @@
         <v>0</v>
       </c>
       <c r="G16" s="12">
-        <v>0</v>
+        <v>1257500</v>
       </c>
       <c r="H16" s="12">
-        <v>0</v>
+        <v>895200</v>
       </c>
       <c r="I16" s="12">
-        <v>0</v>
+        <v>1289750</v>
       </c>
       <c r="J16" s="12">
-        <v>0</v>
+        <v>490000</v>
       </c>
       <c r="K16" s="12">
-        <v>0</v>
+        <v>433000</v>
       </c>
       <c r="L16" s="12">
-        <v>0</v>
+        <v>921000</v>
       </c>
       <c r="M16" s="12">
-        <v>0</v>
+        <v>385000</v>
       </c>
       <c r="N16" s="12">
-        <v>0</v>
+        <v>1332000</v>
       </c>
       <c r="O16" s="12">
-        <v>0</v>
+        <v>399000</v>
       </c>
       <c r="P16" s="12">
-        <v>0</v>
+        <v>486000</v>
       </c>
       <c r="Q16" s="12">
-        <v>0</v>
+        <v>1074000</v>
       </c>
       <c r="R16" s="12">
-        <v>0</v>
+        <v>1147000</v>
       </c>
       <c r="S16" s="12">
-        <v>0</v>
+        <v>785000</v>
       </c>
       <c r="T16" s="12">
-        <v>0</v>
+        <v>483000</v>
       </c>
       <c r="U16" s="12">
-        <v>0</v>
+        <v>56000</v>
       </c>
       <c r="V16" s="12">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="W16" s="12">
-        <v>0</v>
+        <v>115000</v>
       </c>
       <c r="X16" s="12">
-        <v>0</v>
+        <v>336000</v>
       </c>
       <c r="Y16" s="12">
-        <v>0</v>
+        <v>787000</v>
       </c>
       <c r="Z16" s="12">
-        <v>0</v>
+        <v>156000</v>
       </c>
       <c r="AA16" s="12">
-        <v>0</v>
+        <v>261000</v>
       </c>
       <c r="AB16" s="12">
-        <v>0</v>
+        <v>319000</v>
       </c>
       <c r="AC16" s="12">
-        <v>0</v>
+        <v>419000</v>
       </c>
       <c r="AD16" s="12">
-        <v>0</v>
+        <v>566000</v>
       </c>
       <c r="AE16" s="13">
         <f>SUM(C16:AD16)</f>
-        <v>0</v>
+        <v>14512450</v>
       </c>
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.25">
@@ -1664,83 +1668,83 @@
         <v>0</v>
       </c>
       <c r="F17" s="12">
-        <v>0</v>
+        <v>104000</v>
       </c>
       <c r="G17" s="12">
-        <v>0</v>
+        <v>600000</v>
       </c>
       <c r="H17" s="12">
-        <v>0</v>
+        <v>642000</v>
       </c>
       <c r="I17" s="12">
-        <v>0</v>
+        <v>810000</v>
       </c>
       <c r="J17" s="12">
-        <v>0</v>
+        <v>326000</v>
       </c>
       <c r="K17" s="12">
-        <v>0</v>
+        <v>335000</v>
       </c>
       <c r="L17" s="12">
-        <v>0</v>
+        <v>552000</v>
       </c>
       <c r="M17" s="12">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="N17" s="12">
-        <v>0</v>
+        <v>353000</v>
       </c>
       <c r="O17" s="12">
-        <v>0</v>
+        <v>346000</v>
       </c>
       <c r="P17" s="12">
-        <v>0</v>
+        <v>178000</v>
       </c>
       <c r="Q17" s="12">
-        <v>0</v>
+        <v>175000</v>
       </c>
       <c r="R17" s="12">
-        <v>0</v>
+        <v>254000</v>
       </c>
       <c r="S17" s="12">
-        <v>0</v>
+        <v>279000</v>
       </c>
       <c r="T17" s="12">
-        <v>0</v>
+        <v>482000</v>
       </c>
       <c r="U17" s="12">
-        <v>0</v>
+        <v>39000</v>
       </c>
       <c r="V17" s="12">
-        <v>0</v>
+        <v>184000</v>
       </c>
       <c r="W17" s="12">
-        <v>0</v>
+        <v>123000</v>
       </c>
       <c r="X17" s="12">
-        <v>0</v>
+        <v>533000</v>
       </c>
       <c r="Y17" s="12">
-        <v>0</v>
+        <v>364000</v>
       </c>
       <c r="Z17" s="12">
-        <v>0</v>
+        <v>357000</v>
       </c>
       <c r="AA17" s="12">
-        <v>0</v>
+        <v>265000</v>
       </c>
       <c r="AB17" s="12">
-        <v>0</v>
+        <v>122000</v>
       </c>
       <c r="AC17" s="12">
-        <v>0</v>
+        <v>415000</v>
       </c>
       <c r="AD17" s="12">
-        <v>0</v>
+        <v>258000</v>
       </c>
       <c r="AE17" s="13">
         <f>SUM(C17:AD17)</f>
-        <v>0</v>
+        <v>8446000</v>
       </c>
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.25">
@@ -1763,49 +1767,49 @@
         <v>0</v>
       </c>
       <c r="G18" s="12">
-        <v>0</v>
+        <v>240000</v>
       </c>
       <c r="H18" s="12">
-        <v>0</v>
+        <v>410000</v>
       </c>
       <c r="I18" s="12">
-        <v>0</v>
+        <v>695000</v>
       </c>
       <c r="J18" s="12">
-        <v>0</v>
+        <v>365000</v>
       </c>
       <c r="K18" s="12">
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="L18" s="12">
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="M18" s="12">
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="N18" s="12">
-        <v>0</v>
+        <v>285000</v>
       </c>
       <c r="O18" s="12">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="P18" s="12">
         <v>0</v>
       </c>
       <c r="Q18" s="12">
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="R18" s="12">
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="S18" s="12">
-        <v>0</v>
+        <v>205000</v>
       </c>
       <c r="T18" s="12">
         <v>0</v>
       </c>
       <c r="U18" s="12">
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="V18" s="12">
         <v>0</v>
@@ -1829,14 +1833,14 @@
         <v>0</v>
       </c>
       <c r="AC18" s="12">
-        <v>0</v>
+        <v>125000</v>
       </c>
       <c r="AD18" s="12">
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="AE18" s="13">
         <f>SUM(C18:AD18)</f>
-        <v>0</v>
+        <v>3525000</v>
       </c>
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.25">
@@ -1859,13 +1863,13 @@
         <v>0</v>
       </c>
       <c r="G19" s="12">
-        <v>0</v>
+        <v>1350000</v>
       </c>
       <c r="H19" s="12">
         <v>0</v>
       </c>
       <c r="I19" s="12">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="J19" s="12">
         <v>0</v>
@@ -1883,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="O19" s="12">
-        <v>0</v>
+        <v>1800000</v>
       </c>
       <c r="P19" s="12">
         <v>0</v>
@@ -1895,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="S19" s="12">
-        <v>0</v>
+        <v>4950000</v>
       </c>
       <c r="T19" s="12">
         <v>0</v>
@@ -1932,7 +1936,7 @@
       </c>
       <c r="AE19" s="13">
         <f>SUM(C19:AD19)</f>
-        <v>0</v>
+        <v>13100000</v>
       </c>
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.25">
@@ -1961,19 +1965,19 @@
         <v>0</v>
       </c>
       <c r="I20" s="12">
-        <v>0</v>
+        <v>420000</v>
       </c>
       <c r="J20" s="12">
-        <v>0</v>
+        <v>630000</v>
       </c>
       <c r="K20" s="12">
         <v>0</v>
       </c>
       <c r="L20" s="12">
-        <v>0</v>
+        <v>420000</v>
       </c>
       <c r="M20" s="12">
-        <v>0</v>
+        <v>210000</v>
       </c>
       <c r="N20" s="12">
         <v>0</v>
@@ -1988,13 +1992,13 @@
         <v>0</v>
       </c>
       <c r="R20" s="12">
-        <v>0</v>
+        <v>420000</v>
       </c>
       <c r="S20" s="12">
         <v>0</v>
       </c>
       <c r="T20" s="12">
-        <v>0</v>
+        <v>210000</v>
       </c>
       <c r="U20" s="12">
         <v>0</v>
@@ -2003,7 +2007,7 @@
         <v>0</v>
       </c>
       <c r="W20" s="12">
-        <v>0</v>
+        <v>420000</v>
       </c>
       <c r="X20" s="12">
         <v>0</v>
@@ -2012,10 +2016,10 @@
         <v>0</v>
       </c>
       <c r="Z20" s="12">
-        <v>0</v>
+        <v>210000</v>
       </c>
       <c r="AA20" s="12">
-        <v>0</v>
+        <v>210000</v>
       </c>
       <c r="AB20" s="12">
         <v>0</v>
@@ -2028,7 +2032,7 @@
       </c>
       <c r="AE20" s="13">
         <f>SUM(C20:AD20)</f>
-        <v>0</v>
+        <v>3150000</v>
       </c>
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.25">
@@ -2054,7 +2058,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="12">
-        <v>0</v>
+        <v>780000</v>
       </c>
       <c r="I21" s="12">
         <v>0</v>
@@ -2075,7 +2079,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="12">
-        <v>0</v>
+        <v>780000</v>
       </c>
       <c r="P21" s="12">
         <v>0</v>
@@ -2084,7 +2088,7 @@
         <v>0</v>
       </c>
       <c r="R21" s="12">
-        <v>0</v>
+        <v>260000</v>
       </c>
       <c r="S21" s="12">
         <v>0</v>
@@ -2124,7 +2128,7 @@
       </c>
       <c r="AE21" s="13">
         <f>SUM(C21:AD21)</f>
-        <v>0</v>
+        <v>1820000</v>
       </c>
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.25">
@@ -2150,19 +2154,19 @@
         <v>0</v>
       </c>
       <c r="H22" s="12">
-        <v>0</v>
+        <v>480000</v>
       </c>
       <c r="I22" s="12">
-        <v>0</v>
+        <v>240000</v>
       </c>
       <c r="J22" s="12">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="K22" s="12">
         <v>0</v>
       </c>
       <c r="L22" s="12">
-        <v>0</v>
+        <v>240000</v>
       </c>
       <c r="M22" s="12">
         <v>0</v>
@@ -2195,7 +2199,7 @@
         <v>0</v>
       </c>
       <c r="W22" s="12">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="X22" s="12">
         <v>0</v>
@@ -2204,7 +2208,7 @@
         <v>0</v>
       </c>
       <c r="Z22" s="12">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="AA22" s="12">
         <v>0</v>
@@ -2220,7 +2224,7 @@
       </c>
       <c r="AE22" s="13">
         <f>SUM(C22:AD22)</f>
-        <v>0</v>
+        <v>1320000</v>
       </c>
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.25">
@@ -2249,10 +2253,10 @@
         <v>0</v>
       </c>
       <c r="I23" s="12">
-        <v>0</v>
+        <v>240000</v>
       </c>
       <c r="J23" s="12">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="K23" s="12">
         <v>0</v>
@@ -2276,13 +2280,13 @@
         <v>0</v>
       </c>
       <c r="R23" s="12">
-        <v>0</v>
+        <v>65000</v>
       </c>
       <c r="S23" s="12">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="T23" s="12">
-        <v>0</v>
+        <v>70000</v>
       </c>
       <c r="U23" s="12">
         <v>0</v>
@@ -2316,7 +2320,7 @@
       </c>
       <c r="AE23" s="13">
         <f>SUM(C23:AD23)</f>
-        <v>0</v>
+        <v>495000</v>
       </c>
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.25">
@@ -2501,14 +2505,14 @@
         <v>0</v>
       </c>
       <c r="AC25" s="12">
-        <v>0</v>
+        <v>180000</v>
       </c>
       <c r="AD25" s="12">
         <v>0</v>
       </c>
       <c r="AE25" s="13">
         <f>SUM(C25:AD25)</f>
-        <v>0</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="26" ht="17.65" customHeight="1" spans="1:31" x14ac:dyDescent="0.25">
@@ -2530,107 +2534,107 @@
       </c>
       <c r="F26" s="15">
         <f>SUM(F6:F25)</f>
-        <v>0</v>
+        <v>104000</v>
       </c>
       <c r="G26" s="15">
         <f>SUM(G6:G25)</f>
-        <v>0</v>
+        <v>3547500</v>
       </c>
       <c r="H26" s="15">
         <f>SUM(H6:H25)</f>
-        <v>0</v>
+        <v>3692200</v>
       </c>
       <c r="I26" s="15">
         <f>SUM(I6:I25)</f>
-        <v>0</v>
+        <v>8974750</v>
       </c>
       <c r="J26" s="15">
         <f>SUM(J6:J25)</f>
-        <v>4460000</v>
+        <v>6721000</v>
       </c>
       <c r="K26" s="15">
         <f>SUM(K6:K25)</f>
-        <v>4872500</v>
+        <v>6130500</v>
       </c>
       <c r="L26" s="15">
         <f>SUM(L6:L25)</f>
-        <v>9270000</v>
+        <v>12143000</v>
       </c>
       <c r="M26" s="15">
         <f>SUM(M6:M25)</f>
-        <v>4550000</v>
+        <v>6075000</v>
       </c>
       <c r="N26" s="15">
         <f>SUM(N6:N25)</f>
-        <v>7150000</v>
+        <v>9520000</v>
       </c>
       <c r="O26" s="15">
         <f>SUM(O6:O25)</f>
-        <v>5550000</v>
+        <v>9460000</v>
       </c>
       <c r="P26" s="15">
         <f>SUM(P6:P25)</f>
-        <v>4104000</v>
+        <v>4848000</v>
       </c>
       <c r="Q26" s="15">
         <f>SUM(Q6:Q25)</f>
-        <v>4854000</v>
+        <v>6518000</v>
       </c>
       <c r="R26" s="15">
         <f>SUM(R6:R25)</f>
-        <v>8140000</v>
+        <v>11326000</v>
       </c>
       <c r="S26" s="15">
         <f>SUM(S6:S25)</f>
-        <v>8228000</v>
+        <v>15217000</v>
       </c>
       <c r="T26" s="15">
         <f>SUM(T6:T25)</f>
-        <v>3110000</v>
+        <v>4630000</v>
       </c>
       <c r="U26" s="15">
         <f>SUM(U6:U25)</f>
-        <v>2700000</v>
+        <v>3275000</v>
       </c>
       <c r="V26" s="15">
         <f>SUM(V6:V25)</f>
-        <v>4100000</v>
+        <v>4654000</v>
       </c>
       <c r="W26" s="15">
         <f>SUM(W6:W25)</f>
-        <v>5015000</v>
+        <v>6073000</v>
       </c>
       <c r="X26" s="15">
         <f>SUM(X6:X25)</f>
-        <v>6430000</v>
+        <v>7729000</v>
       </c>
       <c r="Y26" s="15">
         <f>SUM(Y6:Y25)</f>
-        <v>4500000</v>
+        <v>5861000</v>
       </c>
       <c r="Z26" s="15">
         <f>SUM(Z6:Z25)</f>
-        <v>4865000</v>
+        <v>5938000</v>
       </c>
       <c r="AA26" s="15">
         <f>SUM(AA6:AA25)</f>
-        <v>4347500</v>
+        <v>5173500</v>
       </c>
       <c r="AB26" s="15">
         <f>SUM(AB6:AB25)</f>
-        <v>2767500</v>
+        <v>3208500</v>
       </c>
       <c r="AC26" s="15">
         <f>SUM(AC6:AC25)</f>
-        <v>4380000</v>
+        <v>5899000</v>
       </c>
       <c r="AD26" s="16">
         <f>SUM(AD6:AD25)</f>
-        <v>4200000</v>
+        <v>5374000</v>
       </c>
       <c r="AE26" s="17">
         <f>SUM(AE6:AE25)</f>
-        <v>107593500</v>
+        <v>162091950</v>
       </c>
     </row>
   </sheetData>
